--- a/结果提交表-已填写.xlsx
+++ b/结果提交表-已填写.xlsx
@@ -1347,7 +1347,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S002-C-1</t>
+          <t>S002-B-1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1357,28 +1357,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>S002-WAT-01;S002-FOD-01;S002-FOD-02;S002-HYG-01;S002-MED-01</t>
+          <t>S002-WAT-01;S002-FOD-01;S002-MED-01</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.13</v>
+        <v>0.067</v>
       </c>
       <c r="G4" t="n">
-        <v>2048.814</v>
+        <v>1822.941</v>
       </c>
       <c r="H4" t="n">
-        <v>5.187445</v>
+        <v>2.722509</v>
       </c>
       <c r="I4" t="n">
-        <v>35.1569</v>
+        <v>31.9373</v>
       </c>
     </row>
     <row r="5">
@@ -1399,29 +1399,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S002-WAT-02;S002-WAT-03;S002-WAT-04</t>
+          <t>S002-WAT-02;S002-WAT-03;S002-WAT-04;S002-FOD-02;S002-HYG-01</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>0.081</v>
+        <v>0.144</v>
       </c>
       <c r="G5" t="n">
-        <v>1916.814</v>
+        <v>2048.814</v>
       </c>
       <c r="H5" t="n">
-        <v>5.26542</v>
+        <v>5.739482</v>
       </c>
       <c r="I5" t="n">
-        <v>34.1822</v>
+        <v>28.2565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S003-C-1</t>
+          <t>S003-B-1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1431,28 +1431,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S003-WAT-01;S003-FOD-01;S003-FOD-02;S003-HYG-01;S003-MED-01</t>
+          <t>S003-WAT-01;S003-FOD-01;S003-MED-01</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F6" t="n">
-        <v>0.13</v>
+        <v>0.067</v>
       </c>
       <c r="G6" t="n">
-        <v>2370.647</v>
+        <v>2081.079</v>
       </c>
       <c r="H6" t="n">
-        <v>5.211934</v>
+        <v>2.781328</v>
       </c>
       <c r="I6" t="n">
-        <v>34.8508</v>
+        <v>30.4668</v>
       </c>
     </row>
     <row r="7">
@@ -1473,23 +1473,23 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S003-WAT-02;S003-WAT-03;S003-WAT-04</t>
+          <t>S003-WAT-02;S003-WAT-03;S003-WAT-04;S003-FOD-02;S003-HYG-01</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>0.081</v>
+        <v>0.144</v>
       </c>
       <c r="G7" t="n">
-        <v>2238.647</v>
+        <v>2370.647</v>
       </c>
       <c r="H7" t="n">
-        <v>5.29106</v>
+        <v>5.768031</v>
       </c>
       <c r="I7" t="n">
-        <v>33.8617</v>
+        <v>27.8996</v>
       </c>
     </row>
     <row r="8">
@@ -4828,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>816.169</v>
+        <v>816.669</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>817.168</v>
+        <v>816.669</v>
       </c>
       <c r="D5" t="n">
-        <v>1759.294</v>
+        <v>1759.794</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1760.293</v>
+        <v>1759.794</v>
       </c>
       <c r="D6" t="n">
         <v>2114.814</v>
@@ -4908,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>752.503</v>
+        <v>753.003</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4931,10 +4931,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>753.502</v>
+        <v>753.003</v>
       </c>
       <c r="D8" t="n">
-        <v>807.442</v>
+        <v>807.941</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>808.441</v>
+        <v>807.941</v>
       </c>
       <c r="D9" t="n">
-        <v>1506.063</v>
+        <v>1506.563</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4987,10 +4987,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1507.062</v>
+        <v>1506.563</v>
       </c>
       <c r="D10" t="n">
-        <v>1561.002</v>
+        <v>1561.501</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1562.001</v>
+        <v>1561.501</v>
       </c>
       <c r="D11" t="n">
         <v>1944.463</v>
@@ -5044,7 +5044,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>836.872</v>
+        <v>837.371</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>837.871</v>
+        <v>837.371</v>
       </c>
       <c r="D13" t="n">
-        <v>1458.229</v>
+        <v>1458.728</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1459.228</v>
+        <v>1458.728</v>
       </c>
       <c r="D14" t="n">
         <v>1965.956</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>776.842</v>
+        <v>777.341</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>777.841</v>
+        <v>777.341</v>
       </c>
       <c r="D16" t="n">
-        <v>1167.714</v>
+        <v>1168.213</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1168.712</v>
+        <v>1168.213</v>
       </c>
       <c r="D17" t="n">
         <v>1603.224</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>821.354</v>
+        <v>821.853</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -5227,10 +5227,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>822.353</v>
+        <v>821.853</v>
       </c>
       <c r="D19" t="n">
-        <v>1630.486</v>
+        <v>1630.986</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1631.485</v>
+        <v>1630.986</v>
       </c>
       <c r="D20" t="n">
         <v>2065.997</v>
@@ -5284,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>749.875</v>
+        <v>750.374</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -5307,10 +5307,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>750.874</v>
+        <v>750.374</v>
       </c>
       <c r="D22" t="n">
-        <v>1607.608</v>
+        <v>1608.108</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1608.607</v>
+        <v>1608.108</v>
       </c>
       <c r="D23" t="n">
         <v>2010.716</v>
@@ -5364,7 +5364,7 @@
         <v>1210.258</v>
       </c>
       <c r="D24" t="n">
-        <v>1979.885</v>
+        <v>1980.384</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -5387,10 +5387,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1980.883</v>
+        <v>1980.384</v>
       </c>
       <c r="D25" t="n">
-        <v>3057.747</v>
+        <v>3058.246</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -5415,7 +5415,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3058.746</v>
+        <v>3058.246</v>
       </c>
       <c r="D26" t="n">
         <v>3494.112</v>
@@ -5444,7 +5444,7 @@
         <v>1495.327</v>
       </c>
       <c r="D27" t="n">
-        <v>2920.804</v>
+        <v>2921.303</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2921.802</v>
+        <v>2921.303</v>
       </c>
       <c r="D28" t="n">
-        <v>2965.723</v>
+        <v>2966.222</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2966.721</v>
+        <v>2966.222</v>
       </c>
       <c r="D29" t="n">
-        <v>2982.688</v>
+        <v>2983.187</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -5521,10 +5521,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2983.686</v>
+        <v>2983.187</v>
       </c>
       <c r="D30" t="n">
-        <v>3997.611</v>
+        <v>3998.11</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5549,7 +5549,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3998.609</v>
+        <v>3998.11</v>
       </c>
       <c r="D31" t="n">
         <v>4482.252</v>
@@ -5578,7 +5578,7 @@
         <v>1603.224</v>
       </c>
       <c r="D32" t="n">
-        <v>2939.432</v>
+        <v>2939.932</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2940.431</v>
+        <v>2939.932</v>
       </c>
       <c r="D33" t="n">
-        <v>3540.361</v>
+        <v>3540.861</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3541.361</v>
+        <v>3540.861</v>
       </c>
       <c r="D34" t="n">
         <v>4045.818</v>
@@ -5658,7 +5658,7 @@
         <v>2243.228</v>
       </c>
       <c r="D35" t="n">
-        <v>3083.726</v>
+        <v>3084.225</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -5681,10 +5681,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3084.724</v>
+        <v>3084.225</v>
       </c>
       <c r="D36" t="n">
-        <v>3263.487</v>
+        <v>3263.987</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3264.487</v>
+        <v>3263.987</v>
       </c>
       <c r="D37" t="n">
-        <v>3498.414</v>
+        <v>3498.911</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5737,10 +5737,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3499.408</v>
+        <v>3498.911</v>
       </c>
       <c r="D38" t="n">
-        <v>3668.91</v>
+        <v>3669.41</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3669.909</v>
+        <v>3669.41</v>
       </c>
       <c r="D39" t="n">
         <v>4168.443</v>
@@ -5794,7 +5794,7 @@
         <v>1965.956</v>
       </c>
       <c r="D40" t="n">
-        <v>2778.898</v>
+        <v>2779.397</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2779.896</v>
+        <v>2779.397</v>
       </c>
       <c r="D41" t="n">
-        <v>3200.109</v>
+        <v>3200.608</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3201.107</v>
+        <v>3200.608</v>
       </c>
       <c r="D42" t="n">
         <v>3678.992</v>
@@ -5874,7 +5874,7 @@
         <v>7829.631</v>
       </c>
       <c r="D43" t="n">
-        <v>9338.16</v>
+        <v>9338.659</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -5897,10 +5897,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9339.157999999999</v>
+        <v>9338.659</v>
       </c>
       <c r="D44" t="n">
-        <v>10367.014</v>
+        <v>10367.513</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10368.012</v>
+        <v>10367.513</v>
       </c>
       <c r="D45" t="n">
         <v>10853.317</v>
@@ -5954,7 +5954,7 @@
         <v>4830.564</v>
       </c>
       <c r="D46" t="n">
-        <v>5589.178</v>
+        <v>5589.677</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5590.176</v>
+        <v>5589.677</v>
       </c>
       <c r="D47" t="n">
-        <v>5925.578</v>
+        <v>5926.077</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5926.577</v>
+        <v>5926.077</v>
       </c>
       <c r="D48" t="n">
-        <v>5931.567</v>
+        <v>5932.065</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5932.563</v>
+        <v>5932.065</v>
       </c>
       <c r="D49" t="n">
-        <v>6145.219</v>
+        <v>6145.71</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -6059,10 +6059,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6146.201</v>
+        <v>6145.71</v>
       </c>
       <c r="D50" t="n">
-        <v>6379.901</v>
+        <v>6380.398</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -6087,10 +6087,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6380.895</v>
+        <v>6380.398</v>
       </c>
       <c r="D51" t="n">
-        <v>6550.398</v>
+        <v>6550.897</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6551.396</v>
+        <v>6550.897</v>
       </c>
       <c r="D52" t="n">
         <v>7049.93</v>
@@ -6144,7 +6144,7 @@
         <v>7956.535</v>
       </c>
       <c r="D53" t="n">
-        <v>8664.316000000001</v>
+        <v>8664.816000000001</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8665.315000000001</v>
+        <v>8664.816000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>8757.177</v>
+        <v>8757.675999999999</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -6195,10 +6195,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8758.174999999999</v>
+        <v>8757.675999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>9187.328</v>
+        <v>9187.826999999999</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9188.326999999999</v>
+        <v>9187.826999999999</v>
       </c>
       <c r="D56" t="n">
         <v>9517.143</v>
@@ -6252,7 +6252,7 @@
         <v>4482.252</v>
       </c>
       <c r="D57" t="n">
-        <v>5427.619</v>
+        <v>5428.118</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5428.617</v>
+        <v>5428.118</v>
       </c>
       <c r="D58" t="n">
-        <v>6505.124</v>
+        <v>6505.624</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6506.123</v>
+        <v>6505.624</v>
       </c>
       <c r="D59" t="n">
         <v>6984.9</v>
@@ -6332,7 +6332,7 @@
         <v>5138.5</v>
       </c>
       <c r="D60" t="n">
-        <v>6562.887</v>
+        <v>6563.386</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -6355,10 +6355,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6563.885</v>
+        <v>6563.386</v>
       </c>
       <c r="D61" t="n">
-        <v>7415.036</v>
+        <v>7415.535</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7416.035</v>
+        <v>7415.535</v>
       </c>
       <c r="D62" t="n">
         <v>7829.631</v>
@@ -6412,7 +6412,7 @@
         <v>5499.77</v>
       </c>
       <c r="D63" t="n">
-        <v>6258.383</v>
+        <v>6258.882</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6259.381</v>
+        <v>6258.882</v>
       </c>
       <c r="D64" t="n">
-        <v>6594.783</v>
+        <v>6595.282</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -6463,10 +6463,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6595.782</v>
+        <v>6595.282</v>
       </c>
       <c r="D65" t="n">
-        <v>6600.772</v>
+        <v>6601.27</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6601.768</v>
+        <v>6601.27</v>
       </c>
       <c r="D66" t="n">
-        <v>6814.424</v>
+        <v>6814.915</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6815.406</v>
+        <v>6814.915</v>
       </c>
       <c r="D67" t="n">
-        <v>7049.106</v>
+        <v>7049.603</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7050.1</v>
+        <v>7049.603</v>
       </c>
       <c r="D68" t="n">
-        <v>7219.603</v>
+        <v>7220.102</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7220.601</v>
+        <v>7220.102</v>
       </c>
       <c r="D69" t="n">
         <v>7719.135</v>
@@ -6602,7 +6602,7 @@
         <v>7410.329</v>
       </c>
       <c r="D70" t="n">
-        <v>8212.191000000001</v>
+        <v>8212.690000000001</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -6625,10 +6625,10 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8213.189</v>
+        <v>8212.690000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>8755.253000000001</v>
+        <v>8755.752</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8756.251</v>
+        <v>8755.752</v>
       </c>
       <c r="D72" t="n">
         <v>9157.983</v>
@@ -6853,7 +6853,7 @@
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>

--- a/结果提交表-已填写.xlsx
+++ b/结果提交表-已填写.xlsx
@@ -1947,7 +1947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
     <col width="12" customWidth="1" style="3" min="1" max="2"/>
@@ -2028,14 +2028,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1210.258</v>
+        <v>1210.482</v>
       </c>
       <c r="H2" t="n">
-        <v>1.076816</v>
+        <v>1.13897</v>
       </c>
     </row>
     <row r="3">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CB0</t>
+          <t>AB0</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -2064,14 +2064,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1495.327</v>
+        <v>1316.642</v>
       </c>
       <c r="H3" t="n">
-        <v>3.003954</v>
+        <v>1.31237</v>
       </c>
     </row>
     <row r="4">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CB1</t>
+          <t>CB0</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -2100,14 +2100,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2114.814</v>
+        <v>1495.327</v>
       </c>
       <c r="H4" t="n">
-        <v>6.125102</v>
+        <v>2.620441</v>
       </c>
     </row>
     <row r="5">
@@ -2118,17 +2118,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BB1</t>
+          <t>CB1</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1944.463</v>
+        <v>2114.814</v>
       </c>
       <c r="H5" t="n">
-        <v>2.764445</v>
+        <v>6.125102</v>
       </c>
     </row>
     <row r="6">
@@ -2154,17 +2154,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AB0</t>
+          <t>BB1</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -2172,14 +2172,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1965.956</v>
+        <v>1560.608</v>
       </c>
       <c r="H6" t="n">
-        <v>2.280251</v>
+        <v>2.101973</v>
       </c>
     </row>
     <row r="7">
@@ -2208,14 +2208,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1603.224</v>
+        <v>1713.036</v>
       </c>
       <c r="H7" t="n">
-        <v>2.022753</v>
+        <v>1.90038</v>
       </c>
     </row>
     <row r="8">
@@ -2244,14 +2244,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S010-&gt;S013</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2065.997</v>
+        <v>1316.642</v>
       </c>
       <c r="H8" t="n">
-        <v>2.287176</v>
+        <v>1.357876</v>
       </c>
     </row>
     <row r="9">
@@ -2280,14 +2280,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S010-&gt;S014</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2010.716</v>
+        <v>2307.348</v>
       </c>
       <c r="H9" t="n">
-        <v>2.929678</v>
+        <v>2.516233</v>
       </c>
     </row>
     <row r="10">
@@ -2312,18 +2312,18 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1210.258</v>
+        <v>1210.482</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>S015-&gt;S003</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3494.112</v>
+        <v>2711.957</v>
       </c>
       <c r="H10" t="n">
-        <v>3.089979</v>
+        <v>1.822105</v>
       </c>
     </row>
     <row r="11">
@@ -2334,32 +2334,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CB2</t>
+          <t>AB4</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1495.327</v>
+        <v>1316.642</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S006-&gt;S007-&gt;S015</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4482.252</v>
+        <v>2628.989</v>
       </c>
       <c r="H11" t="n">
-        <v>5.823993</v>
+        <v>1.267708</v>
       </c>
     </row>
     <row r="12">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U02</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2380,22 +2380,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AB4</t>
+          <t>AB5</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1603.224</v>
+        <v>1316.642</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S006-&gt;S015</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4045.818</v>
+        <v>3029.678</v>
       </c>
       <c r="H12" t="n">
-        <v>2.809999</v>
+        <v>1.965803</v>
       </c>
     </row>
     <row r="13">
@@ -2406,32 +2406,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BB3</t>
+          <t>CB2</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1944.463</v>
+        <v>1495.327</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S001-&gt;S010</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3869.678</v>
+        <v>3814.962</v>
       </c>
       <c r="H13" t="n">
-        <v>2.677141</v>
+        <v>4.687767</v>
       </c>
     </row>
     <row r="14">
@@ -2442,32 +2442,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AB5</t>
+          <t>BB3</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1965.956</v>
+        <v>1560.608</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3678.992</v>
+        <v>3505.071</v>
       </c>
       <c r="H14" t="n">
-        <v>1.90038</v>
+        <v>2.764445</v>
       </c>
     </row>
     <row r="15">
@@ -2496,14 +2496,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S001-&gt;S010-&gt;S014</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5138.5</v>
+        <v>4617.461</v>
       </c>
       <c r="H15" t="n">
-        <v>5.434619</v>
+        <v>6.327428</v>
       </c>
     </row>
     <row r="16">
@@ -2514,32 +2514,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BB0</t>
+          <t>AB0</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3494.112</v>
+        <v>2195.771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S005-&gt;S004</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>5713.478</v>
+        <v>4161.727</v>
       </c>
       <c r="H16" t="n">
-        <v>2.848879</v>
+        <v>2.358382</v>
       </c>
     </row>
     <row r="17">
@@ -2550,32 +2550,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BB1</t>
+          <t>AB2</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3869.678</v>
+        <v>2307.348</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5430.286</v>
+        <v>4318.065</v>
       </c>
       <c r="H17" t="n">
-        <v>2.101973</v>
+        <v>2.929678</v>
       </c>
     </row>
     <row r="18">
@@ -2586,32 +2586,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CB0</t>
+          <t>BB0</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4482.252</v>
+        <v>2711.957</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>6984.9</v>
+        <v>4637.171</v>
       </c>
       <c r="H18" t="n">
-        <v>6.327428</v>
+        <v>2.677141</v>
       </c>
     </row>
     <row r="19">
@@ -2622,32 +2622,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CB1</t>
+          <t>AB1</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5138.5</v>
+        <v>2762.035</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>S011-&gt;S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7829.631</v>
+        <v>4945.299</v>
       </c>
       <c r="H19" t="n">
-        <v>6.373347</v>
+        <v>3.201668</v>
       </c>
     </row>
     <row r="20">
@@ -2658,32 +2658,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BB2</t>
+          <t>AB4</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5499.77</v>
+        <v>3495.216</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>S005-&gt;S004</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>7719.135</v>
+        <v>5148.252</v>
       </c>
       <c r="H20" t="n">
-        <v>2.906122</v>
+        <v>1.801313</v>
       </c>
     </row>
     <row r="21">
@@ -2694,32 +2694,176 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BB1</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3505.071</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S004</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>5430.286</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.584988</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>U07</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CB2</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>6984.9</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CB0</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3814.962</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S011-&gt;S008</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>6506.093</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.373347</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AB3</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4161.727</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>6365.051</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.933015</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>U08</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CB1</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4617.461</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>S005</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>8732.554</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.928598</v>
+      <c r="G24" t="n">
+        <v>6497.115</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.236459</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BB2</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4637.171</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S015</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>6466.949</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.311387</v>
       </c>
     </row>
   </sheetData>
@@ -2767,7 +2911,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S001-MED-02</t>
+          <t>S006-WAT-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2777,17 +2921,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>918.252</v>
+        <v>884.004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S001-MED-01</t>
+          <t>S006-HYG-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2797,37 +2941,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>918.252</v>
+        <v>884.004</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S001-WAT-01</t>
+          <t>S006-WAT-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T01</t>
+          <t>T02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>918.252</v>
+        <v>937.0839999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S001-WAT-03</t>
+          <t>S006-MED-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2837,22 +2981,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1182.849</v>
+        <v>937.0839999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S001-WAT-05</t>
+          <t>S001-WAT-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2867,12 +3011,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S001-WAT-06</t>
+          <t>S001-WAT-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2887,12 +3031,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S001-WAT-02</t>
+          <t>S001-WAT-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2907,12 +3051,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S001-FOD-01</t>
+          <t>S001-FOD-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2927,12 +3071,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S001-WAT-04</t>
+          <t>S001-FOD-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T02</t>
+          <t>T03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2947,7 +3091,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S002-FOD-02</t>
+          <t>S001-FOD-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2957,11 +3101,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1490.817</v>
+        <v>1182.849</v>
       </c>
     </row>
     <row r="12">
@@ -2972,7 +3116,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2987,12 +3131,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S002-WAT-02</t>
+          <t>S002-HYG-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3007,12 +3151,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S002-WAT-03</t>
+          <t>S002-WAT-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3027,12 +3171,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S002-HYG-01</t>
+          <t>S002-WAT-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3047,12 +3191,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S002-FOD-01</t>
+          <t>S002-FOD-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3067,7 +3211,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S012-MED-01</t>
+          <t>S002-FOD-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3077,57 +3221,57 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1282.162</v>
+        <v>1490.817</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S012-WAT-01</t>
+          <t>S009-WAT-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1282.162</v>
+        <v>1091.894</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S012-FOD-01</t>
+          <t>S009-MED-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1282.162</v>
+        <v>1091.894</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S014-MED-01</t>
+          <t>S009-FOD-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3137,37 +3281,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1260.534</v>
+        <v>1091.894</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S014-WAT-01</t>
+          <t>S007-MED-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1260.534</v>
+        <v>1134.158</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S013-WAT-01</t>
+          <t>S007-WAT-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3177,37 +3321,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1079.146</v>
+        <v>1134.158</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S013-FOD-01</t>
+          <t>S006-FOD-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1079.146</v>
+        <v>937.0839999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S010-WAT-01</t>
+          <t>S006-WAT-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3217,11 +3361,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1134.906</v>
+        <v>937.0839999999999</v>
       </c>
     </row>
     <row r="25">
@@ -3232,7 +3376,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3247,27 +3391,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S013-MED-01</t>
+          <t>S010-WAT-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1541.918</v>
+        <v>1134.906</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S002-WAT-01</t>
+          <t>S014-MED-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3277,37 +3421,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1287.298</v>
+        <v>1601.927</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S002-MED-01</t>
+          <t>S013-WAT-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1287.298</v>
+        <v>2268.753</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S015-WAT-01</t>
+          <t>S013-MED-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3317,17 +3461,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2338.587</v>
+        <v>2268.753</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S003-WAT-01</t>
+          <t>S013-FOD-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3337,17 +3481,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S013</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2761.546</v>
+        <v>2268.753</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S006-WAT-03</t>
+          <t>S001-MED-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3357,17 +3501,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2694.741</v>
+        <v>2285.939</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S006-WAT-02</t>
+          <t>S001-WAT-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3377,17 +3521,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2694.741</v>
+        <v>2285.939</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S006-FOD-01</t>
+          <t>S001-MED-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3397,42 +3541,42 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2694.741</v>
+        <v>2285.939</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S006-HYG-01</t>
+          <t>S007-WAT-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2694.741</v>
+        <v>2450.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S007-WAT-02</t>
+          <t>S007-FOD-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3441,133 +3585,133 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3379.455</v>
+        <v>2450.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S007-FOD-01</t>
+          <t>S001-WAT-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3379.455</v>
+        <v>2708.176</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S007-HYG-01</t>
+          <t>S001-WAT-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3379.455</v>
+        <v>2708.176</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S015-FOD-01</t>
+          <t>S001-WAT-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3819.907</v>
+        <v>2708.176</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S006-WAT-01</t>
+          <t>S001-WAT-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2570.309</v>
+        <v>2708.176</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S006-MED-01</t>
+          <t>S001-HYG-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2570.309</v>
+        <v>2708.176</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S015-MED-01</t>
+          <t>S001-HYG-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3334.025</v>
+        <v>2708.176</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S004-WAT-01</t>
+          <t>S010-FOD-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3577,37 +3721,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3188.718</v>
+        <v>3308.463</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S004-HYG-01</t>
+          <t>S012-WAT-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3188.718</v>
+        <v>2842.769</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S007-WAT-01</t>
+          <t>S012-MED-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3617,17 +3761,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3100.114</v>
+        <v>2842.769</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S007-MED-01</t>
+          <t>S012-FOD-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3637,17 +3781,17 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3100.114</v>
+        <v>2842.769</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S001-WAT-07</t>
+          <t>S003-MED-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3657,17 +3801,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3357.662</v>
+        <v>3826.598</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S001-WAT-08</t>
+          <t>S003-FOD-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3677,17 +3821,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3357.662</v>
+        <v>3826.598</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S001-FOD-02</t>
+          <t>S003-WAT-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3697,17 +3841,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3357.662</v>
+        <v>3826.598</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S001-FOD-03</t>
+          <t>S003-WAT-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3717,17 +3861,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3357.662</v>
+        <v>3826.598</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S001-HYG-02</t>
+          <t>S003-WAT-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3737,17 +3881,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3357.662</v>
+        <v>3826.598</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S001-HYG-01</t>
+          <t>S003-FOD-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3757,17 +3901,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3357.662</v>
+        <v>3826.598</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S010-FOD-01</t>
+          <t>S003-HYG-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3777,22 +3921,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3957.949</v>
+        <v>3826.598</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S014-FOD-01</t>
+          <t>S014-WAT-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3801,13 +3945,13 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4463.613</v>
+        <v>3456.305</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S004-MED-01</t>
+          <t>S014-FOD-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3817,262 +3961,262 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5032.517</v>
+        <v>3456.305</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S004-WAT-02</t>
+          <t>S002-WAT-01</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5032.517</v>
+        <v>3594.647</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S005-FOD-01</t>
+          <t>S002-MED-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4536.186</v>
+        <v>3594.647</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S009-WAT-01</t>
+          <t>S004-WAT-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4961.572</v>
+        <v>3956.211</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S009-MED-01</t>
+          <t>S004-HYG-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4961.572</v>
+        <v>3956.211</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S009-FOD-01</t>
+          <t>S004-WAT-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4961.572</v>
+        <v>4135.313</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S003-FOD-02</t>
+          <t>S004-FOD-01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6194.036</v>
+        <v>4135.313</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S003-FOD-01</t>
+          <t>S007-HYG-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6194.036</v>
+        <v>4569.374</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S003-HYG-01</t>
+          <t>S004-WAT-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>6194.036</v>
+        <v>4749.325</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S003-MED-01</t>
+          <t>S004-MED-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6194.036</v>
+        <v>4749.325</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S003-WAT-03</t>
+          <t>S008-WAT-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6194.036</v>
+        <v>5807.113</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S003-WAT-04</t>
+          <t>S008-MED-01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6194.036</v>
+        <v>5807.113</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S003-WAT-02</t>
+          <t>S008-WAT-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6194.036</v>
+        <v>5807.113</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S008-WAT-01</t>
+          <t>S008-FOD-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4081,18 +4225,18 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>7130.651</v>
+        <v>5807.113</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S008-MED-01</t>
+          <t>S008-HYG-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4101,178 +4245,178 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7130.651</v>
+        <v>5807.113</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S008-WAT-02</t>
+          <t>S011-MED-01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7130.651</v>
+        <v>4939.414</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S008-FOD-01</t>
+          <t>S011-FOD-01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7130.651</v>
+        <v>4939.414</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S008-HYG-01</t>
+          <t>S011-WAT-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>7130.651</v>
+        <v>4939.414</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S011-WAT-01</t>
+          <t>S003-WAT-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>6262.952</v>
+        <v>5511.362</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S011-MED-01</t>
+          <t>S005-WAT-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6262.952</v>
+        <v>5991.923</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S011-FOD-01</t>
+          <t>S005-MED-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6262.952</v>
+        <v>5991.923</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S004-FOD-01</t>
+          <t>S005-WAT-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>7038.175</v>
+        <v>5991.923</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S004-WAT-03</t>
+          <t>S005-WAT-02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>7038.175</v>
+        <v>5991.923</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S005-MED-01</t>
+          <t>S005-HYG-01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4281,18 +4425,18 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6541.843</v>
+        <v>5991.923</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S005-WAT-01</t>
+          <t>S005-FOD-01</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4301,67 +4445,67 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>8227.361999999999</v>
+        <v>5991.923</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S005-HYG-01</t>
+          <t>S015-WAT-01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>8227.361999999999</v>
+        <v>5855.5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S005-WAT-03</t>
+          <t>S015-FOD-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>8227.361999999999</v>
+        <v>5855.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S005-WAT-02</t>
+          <t>S015-MED-01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>8227.361999999999</v>
+        <v>5855.5</v>
       </c>
     </row>
   </sheetData>
@@ -4375,7 +4519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" style="8" min="1" max="1"/>
@@ -4463,28 +4607,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44.754</v>
+        <v>96.59099999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>109.204779</v>
+        <v>109.272123</v>
       </c>
       <c r="F2" t="n">
-        <v>23.050068</v>
+        <v>23.00561</v>
       </c>
       <c r="G2" t="n">
-        <v>681.374</v>
+        <v>597.4450000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>748.876</v>
+        <v>706.783</v>
       </c>
       <c r="I2" t="n">
-        <v>3998.609</v>
+        <v>3654.999</v>
       </c>
       <c r="J2" t="n">
-        <v>4538.871</v>
+        <v>4094.335</v>
       </c>
       <c r="K2" t="n">
-        <v>1.269457</v>
+        <v>1.123258</v>
       </c>
     </row>
     <row r="3">
@@ -4504,28 +4648,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>141.313</v>
+        <v>151.959</v>
       </c>
       <c r="E3" t="n">
-        <v>109.272123</v>
+        <v>109.191579</v>
       </c>
       <c r="F3" t="n">
-        <v>23.00561</v>
+        <v>23.028424</v>
       </c>
       <c r="G3" t="n">
-        <v>597.4450000000001</v>
+        <v>459.03</v>
       </c>
       <c r="H3" t="n">
-        <v>751.504</v>
+        <v>813.074</v>
       </c>
       <c r="I3" t="n">
-        <v>1631.298</v>
+        <v>1235.02</v>
       </c>
       <c r="J3" t="n">
-        <v>2070.635</v>
+        <v>1713.745</v>
       </c>
       <c r="K3" t="n">
-        <v>0.49124</v>
+        <v>0.372932</v>
       </c>
     </row>
     <row r="4">
@@ -4545,28 +4689,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2370.635</v>
+        <v>2013.745</v>
       </c>
       <c r="E4" t="n">
-        <v>109.244675</v>
+        <v>109.226227</v>
       </c>
       <c r="F4" t="n">
-        <v>23.062782</v>
+        <v>23.037053</v>
       </c>
       <c r="G4" t="n">
-        <v>480.909</v>
+        <v>511.089</v>
       </c>
       <c r="H4" t="n">
-        <v>3081.976</v>
+        <v>2533.416</v>
       </c>
       <c r="I4" t="n">
-        <v>3671.659</v>
+        <v>3916.955</v>
       </c>
       <c r="J4" t="n">
-        <v>4202.434</v>
+        <v>4258.575</v>
       </c>
       <c r="K4" t="n">
-        <v>0.475471</v>
+        <v>0.593445</v>
       </c>
     </row>
     <row r="5">
@@ -4577,7 +4721,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4586,28 +4730,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4722.958</v>
+        <v>4394.335</v>
       </c>
       <c r="E5" t="n">
-        <v>109.204779</v>
+        <v>109.191579</v>
       </c>
       <c r="F5" t="n">
-        <v>23.050068</v>
+        <v>23.028424</v>
       </c>
       <c r="G5" t="n">
-        <v>681.374</v>
+        <v>459.03</v>
       </c>
       <c r="H5" t="n">
-        <v>5427.08</v>
+        <v>5055.45</v>
       </c>
       <c r="I5" t="n">
-        <v>8757.249</v>
+        <v>7057.516</v>
       </c>
       <c r="J5" t="n">
-        <v>9297.51</v>
+        <v>7536.242</v>
       </c>
       <c r="K5" t="n">
-        <v>1.294034</v>
+        <v>0.855747</v>
       </c>
     </row>
     <row r="6">
@@ -4618,7 +4762,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4627,28 +4771,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5220.214</v>
+        <v>4558.575</v>
       </c>
       <c r="E6" t="n">
-        <v>109.244675</v>
+        <v>109.237801</v>
       </c>
       <c r="F6" t="n">
-        <v>23.062782</v>
+        <v>23.068897</v>
       </c>
       <c r="G6" t="n">
-        <v>480.909</v>
+        <v>445.42</v>
       </c>
       <c r="H6" t="n">
-        <v>5931.555</v>
+        <v>5297.917</v>
       </c>
       <c r="I6" t="n">
-        <v>7222.351</v>
+        <v>6152.221</v>
       </c>
       <c r="J6" t="n">
-        <v>7753.127</v>
+        <v>6708.04</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6897</v>
+        <v>0.57673</v>
       </c>
     </row>
     <row r="7">
@@ -4659,37 +4803,78 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RC6</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7559.645</v>
+      </c>
+      <c r="E7" t="n">
+        <v>109.249175</v>
+      </c>
+      <c r="F7" t="n">
+        <v>23.058282</v>
+      </c>
+      <c r="G7" t="n">
+        <v>552.175</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8265.189</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8854.871999999999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9385.789000000001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.466721</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>R01</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>RC6</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>8053.127</v>
-      </c>
-      <c r="E7" t="n">
-        <v>109.272123</v>
-      </c>
-      <c r="F7" t="n">
-        <v>23.00561</v>
-      </c>
-      <c r="G7" t="n">
-        <v>597.4450000000001</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8663.317999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10368.012</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10807.348</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.743293</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>RC2</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7836.242</v>
+      </c>
+      <c r="E8" t="n">
+        <v>109.237801</v>
+      </c>
+      <c r="F8" t="n">
+        <v>23.068897</v>
+      </c>
+      <c r="G8" t="n">
+        <v>445.42</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8575.584000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9193.639999999999</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9749.459999999999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.504543</v>
       </c>
     </row>
   </sheetData>
@@ -4703,7 +4888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:W67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" style="8" min="1" max="2"/>
@@ -4776,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1210.258</v>
+        <v>1210.482</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4802,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1495.327</v>
+        <v>1316.642</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4828,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>816.669</v>
+        <v>1495.327</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4842,55 +5027,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>816.669</v>
+        <v>1718.246</v>
       </c>
       <c r="D5" t="n">
-        <v>1759.794</v>
+        <v>2534.914</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T03</t>
+          <t>T04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1759.794</v>
+        <v>2534.914</v>
       </c>
       <c r="D6" t="n">
-        <v>2114.814</v>
+        <v>2678.784</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4901,22 +5086,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2678.784</v>
       </c>
       <c r="D7" t="n">
-        <v>753.003</v>
+        <v>3334.17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4931,10 +5118,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>753.003</v>
+        <v>3334.17</v>
       </c>
       <c r="D8" t="n">
-        <v>807.941</v>
+        <v>3478.04</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4955,78 +5142,76 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>807.941</v>
+        <v>3478.04</v>
       </c>
       <c r="D9" t="n">
-        <v>1506.563</v>
+        <v>3833.06</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1506.563</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1561.501</v>
+        <v>708.28</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T04</t>
+          <t>T05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1561.501</v>
+        <v>708.28</v>
       </c>
       <c r="D11" t="n">
-        <v>1944.463</v>
+        <v>1231.292</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -5041,10 +5226,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1231.292</v>
       </c>
       <c r="D12" t="n">
-        <v>837.371</v>
+        <v>1560.608</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -5058,55 +5243,55 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>837.371</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1458.728</v>
+        <v>813.441</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T05</t>
+          <t>T06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1458.728</v>
+        <v>813.441</v>
       </c>
       <c r="D14" t="n">
-        <v>1965.956</v>
+        <v>1234.653</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -5121,10 +5306,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1234.653</v>
       </c>
       <c r="D15" t="n">
-        <v>777.341</v>
+        <v>1713.036</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -5138,35 +5323,33 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>777.341</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1168.213</v>
+        <v>1316.642</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T06</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5175,10 +5358,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1168.213</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1603.224</v>
+        <v>821.853</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -5192,61 +5375,61 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>821.853</v>
       </c>
       <c r="D18" t="n">
-        <v>821.853</v>
+        <v>1800.121</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>821.853</v>
+        <v>1800.121</v>
       </c>
       <c r="D19" t="n">
-        <v>1630.986</v>
+        <v>2307.348</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>R02</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5255,10 +5438,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1630.986</v>
+        <v>1210.482</v>
       </c>
       <c r="D20" t="n">
-        <v>2065.997</v>
+        <v>1951.925</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -5272,61 +5455,61 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1951.925</v>
       </c>
       <c r="D21" t="n">
-        <v>750.374</v>
+        <v>2342.843</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>750.374</v>
+        <v>2342.843</v>
       </c>
       <c r="D22" t="n">
-        <v>1608.108</v>
+        <v>2711.957</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T08</t>
+          <t>T10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5335,10 +5518,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1608.108</v>
+        <v>1316.642</v>
       </c>
       <c r="D23" t="n">
-        <v>2010.716</v>
+        <v>2628.989</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -5352,7 +5535,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5361,10 +5544,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1210.258</v>
+        <v>1720.342</v>
       </c>
       <c r="D24" t="n">
-        <v>1980.384</v>
+        <v>2533.783</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -5378,7 +5561,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5387,10 +5570,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1980.384</v>
+        <v>2533.783</v>
       </c>
       <c r="D25" t="n">
-        <v>3058.246</v>
+        <v>2954.995</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -5399,14 +5582,14 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>T09</t>
+          <t>T11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5415,10 +5598,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3058.246</v>
+        <v>2954.995</v>
       </c>
       <c r="D26" t="n">
-        <v>3494.112</v>
+        <v>3433.378</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -5432,7 +5615,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5444,7 +5627,7 @@
         <v>1495.327</v>
       </c>
       <c r="D27" t="n">
-        <v>2921.303</v>
+        <v>2974.356</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -5458,7 +5641,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5467,10 +5650,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2921.303</v>
+        <v>2974.356</v>
       </c>
       <c r="D28" t="n">
-        <v>2966.222</v>
+        <v>3397.563</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5486,7 +5669,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5495,10 +5678,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2966.222</v>
+        <v>3397.563</v>
       </c>
       <c r="D29" t="n">
-        <v>2983.187</v>
+        <v>3814.962</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -5512,61 +5695,61 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2983.187</v>
+        <v>1560.608</v>
       </c>
       <c r="D30" t="n">
-        <v>3998.11</v>
+        <v>2313.61</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T10</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3998.11</v>
+        <v>2313.61</v>
       </c>
       <c r="D31" t="n">
-        <v>4482.252</v>
+        <v>3122.109</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5575,10 +5758,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1603.224</v>
+        <v>3122.109</v>
       </c>
       <c r="D32" t="n">
-        <v>2939.932</v>
+        <v>3505.071</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5592,61 +5775,61 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2939.932</v>
+        <v>5033.107</v>
       </c>
       <c r="D33" t="n">
-        <v>3540.861</v>
+        <v>5978.973</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>T11</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3540.861</v>
+        <v>5978.973</v>
       </c>
       <c r="D34" t="n">
-        <v>4045.818</v>
+        <v>7056.478</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>R04</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5655,10 +5838,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2243.228</v>
+        <v>7056.478</v>
       </c>
       <c r="D35" t="n">
-        <v>3084.225</v>
+        <v>7535.754</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -5672,35 +5855,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3084.225</v>
+        <v>2195.771</v>
       </c>
       <c r="D36" t="n">
-        <v>3263.987</v>
+        <v>3033.142</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5709,10 +5890,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3263.987</v>
+        <v>3033.142</v>
       </c>
       <c r="D37" t="n">
-        <v>3498.911</v>
+        <v>3654.499</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5721,42 +5902,40 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3498.911</v>
+        <v>3654.499</v>
       </c>
       <c r="D38" t="n">
-        <v>3669.41</v>
+        <v>4161.727</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5765,10 +5944,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3669.41</v>
+        <v>2307.348</v>
       </c>
       <c r="D39" t="n">
-        <v>4168.443</v>
+        <v>3057.723</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5782,33 +5961,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1965.956</v>
+        <v>3057.723</v>
       </c>
       <c r="D40" t="n">
-        <v>2779.397</v>
+        <v>3237.56</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5817,10 +5998,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2779.397</v>
+        <v>3237.56</v>
       </c>
       <c r="D41" t="n">
-        <v>3200.608</v>
+        <v>3915.456</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -5829,14 +6010,14 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5845,10 +6026,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3200.608</v>
+        <v>3915.456</v>
       </c>
       <c r="D42" t="n">
-        <v>3678.992</v>
+        <v>4318.065</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -5862,7 +6043,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5871,10 +6052,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7829.631</v>
+        <v>7426.441</v>
       </c>
       <c r="D43" t="n">
-        <v>9338.659</v>
+        <v>8267.438</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -5888,7 +6069,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5897,10 +6078,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>9338.659</v>
+        <v>8267.438</v>
       </c>
       <c r="D44" t="n">
-        <v>10367.513</v>
+        <v>8852.623</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -5916,7 +6097,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5925,10 +6106,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10367.513</v>
+        <v>8852.623</v>
       </c>
       <c r="D45" t="n">
-        <v>10853.317</v>
+        <v>9351.656000000001</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -5942,7 +6123,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5951,10 +6132,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4830.564</v>
+        <v>4360.4</v>
       </c>
       <c r="D46" t="n">
-        <v>5589.677</v>
+        <v>5298.417</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -5968,7 +6149,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5977,10 +6158,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5589.677</v>
+        <v>5298.417</v>
       </c>
       <c r="D47" t="n">
-        <v>5926.077</v>
+        <v>5947.611</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -5989,14 +6170,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>R05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6005,10 +6186,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5926.077</v>
+        <v>5947.611</v>
       </c>
       <c r="D48" t="n">
-        <v>5932.065</v>
+        <v>6543.664</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -6022,35 +6203,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5932.065</v>
+        <v>4272.376</v>
       </c>
       <c r="D49" t="n">
-        <v>6145.71</v>
+        <v>5055.817</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6059,10 +6238,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6145.71</v>
+        <v>5055.817</v>
       </c>
       <c r="D50" t="n">
-        <v>6380.398</v>
+        <v>5447.028</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -6071,42 +6250,40 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>R04</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>6380.398</v>
+        <v>5447.028</v>
       </c>
       <c r="D51" t="n">
-        <v>6550.897</v>
+        <v>5925.412</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6115,10 +6292,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>6550.897</v>
+        <v>4459.169</v>
       </c>
       <c r="D52" t="n">
-        <v>7049.93</v>
+        <v>5300.166</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -6132,115 +6309,115 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7956.535</v>
+        <v>5300.166</v>
       </c>
       <c r="D53" t="n">
-        <v>8664.816000000001</v>
+        <v>5885.351</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>R05</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8664.816000000001</v>
+        <v>5885.351</v>
       </c>
       <c r="D54" t="n">
-        <v>8757.675999999999</v>
+        <v>6384.384</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8757.675999999999</v>
+        <v>3874.145</v>
       </c>
       <c r="D55" t="n">
-        <v>9187.826999999999</v>
+        <v>5299.03</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>R06</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>9187.826999999999</v>
+        <v>5299.03</v>
       </c>
       <c r="D56" t="n">
-        <v>9517.143</v>
+        <v>6151.179</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>R05</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6249,10 +6426,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>4482.252</v>
+        <v>6151.179</v>
       </c>
       <c r="D57" t="n">
-        <v>5428.118</v>
+        <v>6565.275</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -6266,61 +6443,61 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5428.118</v>
+        <v>4252.958</v>
       </c>
       <c r="D58" t="n">
-        <v>6505.624</v>
+        <v>5055.949</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6505.624</v>
+        <v>5055.949</v>
       </c>
       <c r="D59" t="n">
-        <v>6984.9</v>
+        <v>5954.351</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>R04</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6329,10 +6506,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5138.5</v>
+        <v>5954.351</v>
       </c>
       <c r="D60" t="n">
-        <v>6563.386</v>
+        <v>6456.282</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -6346,115 +6523,115 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6563.386</v>
+        <v>7714.721</v>
       </c>
       <c r="D61" t="n">
-        <v>7415.535</v>
+        <v>8577.081</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>7415.535</v>
+        <v>8577.081</v>
       </c>
       <c r="D62" t="n">
-        <v>7829.631</v>
+        <v>8685.716</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>5499.77</v>
+        <v>8685.716</v>
       </c>
       <c r="D63" t="n">
-        <v>6258.882</v>
+        <v>9192.144</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>R07</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6258.882</v>
+        <v>9192.144</v>
       </c>
       <c r="D64" t="n">
-        <v>6595.282</v>
+        <v>9594.375</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6463,10 +6640,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6595.282</v>
+        <v>5596.663</v>
       </c>
       <c r="D65" t="n">
-        <v>6601.27</v>
+        <v>6396.789</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -6480,7 +6657,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6489,10 +6666,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6601.27</v>
+        <v>6396.789</v>
       </c>
       <c r="D66" t="n">
-        <v>6814.915</v>
+        <v>6986.709</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -6508,162 +6685,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6814.915</v>
+        <v>6986.709</v>
       </c>
       <c r="D67" t="n">
-        <v>7049.603</v>
+        <v>7426.441</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>R05</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>T19</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>7049.603</v>
-      </c>
-      <c r="D68" t="n">
-        <v>7220.102</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>T19</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>7220.102</v>
-      </c>
-      <c r="D69" t="n">
-        <v>7719.135</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>7410.329</v>
-      </c>
-      <c r="D70" t="n">
-        <v>8212.690000000001</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>8212.690000000001</v>
-      </c>
-      <c r="D71" t="n">
-        <v>8755.752</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>8755.752</v>
-      </c>
-      <c r="D72" t="n">
-        <v>9157.983</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
         <v/>
       </c>
     </row>
@@ -6760,14 +6801,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S008,S010,S011,S013,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S010,S011,S013,S014</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -6776,7 +6817,7 @@
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -6785,7 +6826,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -6797,7 +6838,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S009,S012</t>
+          <t>S009,S012,S015</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -6813,7 +6854,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -6822,7 +6863,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -6834,14 +6875,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S010,S013,S014,S015</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S010,S013,S014</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
@@ -6850,7 +6891,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -6859,7 +6900,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -6908,7 +6949,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S009,S012</t>
+          <t>S009,S012,S015</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -6924,7 +6965,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6933,7 +6974,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/结果提交表-已填写.xlsx
+++ b/结果提交表-已填写.xlsx
@@ -2172,14 +2172,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1560.608</v>
+        <v>1944.463</v>
       </c>
       <c r="H6" t="n">
-        <v>2.101973</v>
+        <v>2.764445</v>
       </c>
     </row>
     <row r="7">
@@ -2456,18 +2456,18 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1560.608</v>
+        <v>1944.463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>3505.071</v>
       </c>
       <c r="H14" t="n">
-        <v>2.764445</v>
+        <v>2.101973</v>
       </c>
     </row>
     <row r="15">
@@ -2604,14 +2604,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>4637.171</v>
+        <v>4541.734</v>
       </c>
       <c r="H18" t="n">
-        <v>2.677141</v>
+        <v>2.311387</v>
       </c>
     </row>
     <row r="19">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3505.071</v>
+        <v>3809.056</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>5430.286</v>
+        <v>5734.271</v>
       </c>
       <c r="H21" t="n">
         <v>2.584988</v>
@@ -2802,32 +2802,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CB1</t>
+          <t>BB2</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4617.461</v>
+        <v>4541.734</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>6497.115</v>
+        <v>6466.949</v>
       </c>
       <c r="H24" t="n">
-        <v>4.236459</v>
+        <v>2.677141</v>
       </c>
     </row>
     <row r="25">
@@ -2838,32 +2838,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BB2</t>
+          <t>CB1</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4637.171</v>
+        <v>4617.461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6466.949</v>
+        <v>6497.115</v>
       </c>
       <c r="H25" t="n">
-        <v>2.311387</v>
+        <v>4.236459</v>
       </c>
     </row>
   </sheetData>
@@ -3231,7 +3231,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S009-WAT-01</t>
+          <t>S012-WAT-01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3241,17 +3241,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1091.894</v>
+        <v>1282.162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S009-MED-01</t>
+          <t>S012-MED-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3261,17 +3261,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1091.894</v>
+        <v>1282.162</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S009-FOD-01</t>
+          <t>S012-FOD-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3281,11 +3281,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1091.894</v>
+        <v>1282.162</v>
       </c>
     </row>
     <row r="21">
@@ -3731,7 +3731,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S012-WAT-01</t>
+          <t>S009-WAT-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2842.769</v>
+        <v>3036.357</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S012-MED-01</t>
+          <t>S009-MED-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3761,17 +3761,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2842.769</v>
+        <v>3036.357</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S012-FOD-01</t>
+          <t>S009-FOD-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3781,11 +3781,11 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2842.769</v>
+        <v>3036.357</v>
       </c>
     </row>
     <row r="46">
@@ -4011,7 +4011,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S004-WAT-03</t>
+          <t>S015-WAT-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3956.211</v>
+        <v>3930.285</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>S004-HYG-01</t>
+          <t>S015-FOD-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4041,37 +4041,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3956.211</v>
+        <v>3930.285</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>S004-WAT-02</t>
+          <t>S015-MED-01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S015</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4135.313</v>
+        <v>3930.285</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S004-FOD-01</t>
+          <t>S004-WAT-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4091,47 +4091,47 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>S007-HYG-01</t>
+          <t>S004-FOD-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>S007</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4569.374</v>
+        <v>4135.313</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S004-WAT-01</t>
+          <t>S007-HYG-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4749.325</v>
+        <v>4569.374</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S004-MED-01</t>
+          <t>S004-WAT-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4145,33 +4145,33 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4749.325</v>
+        <v>5053.31</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S008-WAT-01</t>
+          <t>S004-MED-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>T21</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5807.113</v>
+        <v>5053.31</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S008-MED-01</t>
+          <t>S008-WAT-01</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4191,7 +4191,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S008-WAT-02</t>
+          <t>S008-MED-01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4211,7 +4211,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S008-FOD-01</t>
+          <t>S008-WAT-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S008-HYG-01</t>
+          <t>S008-FOD-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4251,7 +4251,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S011-MED-01</t>
+          <t>S008-HYG-01</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4261,17 +4261,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4939.414</v>
+        <v>5807.113</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S011-FOD-01</t>
+          <t>S011-MED-01</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4291,7 +4291,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S011-WAT-01</t>
+          <t>S011-FOD-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4311,47 +4311,47 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S003-WAT-01</t>
+          <t>S011-WAT-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>5511.362</v>
+        <v>4939.414</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>S005-WAT-01</t>
+          <t>S003-WAT-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>5991.923</v>
+        <v>5511.362</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>S005-MED-01</t>
+          <t>S004-WAT-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4361,17 +4361,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>5991.923</v>
+        <v>5785.988</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>S005-WAT-03</t>
+          <t>S004-HYG-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5991.923</v>
+        <v>5785.988</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>S005-WAT-02</t>
+          <t>S005-WAT-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4411,12 +4411,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>S005-HYG-01</t>
+          <t>S005-MED-01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4431,12 +4431,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>S005-FOD-01</t>
+          <t>S005-WAT-03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4451,7 +4451,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S015-WAT-01</t>
+          <t>S005-WAT-02</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4461,17 +4461,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5855.5</v>
+        <v>5991.923</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S015-FOD-01</t>
+          <t>S005-HYG-01</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5855.5</v>
+        <v>5991.923</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S015-MED-01</t>
+          <t>S005-FOD-01</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4501,11 +4501,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5855.5</v>
+        <v>5991.923</v>
       </c>
     </row>
   </sheetData>
@@ -4607,28 +4607,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>96.59099999999999</v>
+        <v>95.889</v>
       </c>
       <c r="E2" t="n">
-        <v>109.272123</v>
+        <v>109.280623</v>
       </c>
       <c r="F2" t="n">
-        <v>23.00561</v>
+        <v>23.01281</v>
       </c>
       <c r="G2" t="n">
-        <v>597.4450000000001</v>
+        <v>544.187</v>
       </c>
       <c r="H2" t="n">
-        <v>706.783</v>
+        <v>751.504</v>
       </c>
       <c r="I2" t="n">
-        <v>3654.999</v>
+        <v>2344.341</v>
       </c>
       <c r="J2" t="n">
-        <v>4094.335</v>
+        <v>6641.722</v>
       </c>
       <c r="K2" t="n">
-        <v>1.123258</v>
+        <v>1.895548</v>
       </c>
     </row>
     <row r="3">
@@ -4639,37 +4639,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RC2</t>
+          <t>RC1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>151.959</v>
+        <v>95.889</v>
       </c>
       <c r="E3" t="n">
-        <v>109.191579</v>
+        <v>109.279697</v>
       </c>
       <c r="F3" t="n">
-        <v>23.028424</v>
+        <v>23.021939</v>
       </c>
       <c r="G3" t="n">
-        <v>459.03</v>
+        <v>576.798</v>
       </c>
       <c r="H3" t="n">
-        <v>813.074</v>
+        <v>2450.424</v>
       </c>
       <c r="I3" t="n">
-        <v>1235.02</v>
+        <v>3654.999</v>
       </c>
       <c r="J3" t="n">
-        <v>1713.745</v>
+        <v>6641.722</v>
       </c>
       <c r="K3" t="n">
-        <v>0.372932</v>
+        <v>1.895548</v>
       </c>
     </row>
     <row r="4">
@@ -4680,37 +4680,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RC3</t>
+          <t>RC1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2013.745</v>
+        <v>95.889</v>
       </c>
       <c r="E4" t="n">
-        <v>109.226227</v>
+        <v>109.236701</v>
       </c>
       <c r="F4" t="n">
-        <v>23.037053</v>
+        <v>23.067797</v>
       </c>
       <c r="G4" t="n">
-        <v>511.089</v>
+        <v>440.527</v>
       </c>
       <c r="H4" t="n">
-        <v>2533.416</v>
+        <v>4179.538</v>
       </c>
       <c r="I4" t="n">
-        <v>3916.955</v>
+        <v>6096.381</v>
       </c>
       <c r="J4" t="n">
-        <v>4258.575</v>
+        <v>6641.722</v>
       </c>
       <c r="K4" t="n">
-        <v>0.593445</v>
+        <v>1.895548</v>
       </c>
     </row>
     <row r="5">
@@ -4721,37 +4721,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RC4</t>
+          <t>RC2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4394.335</v>
+        <v>108.952</v>
       </c>
       <c r="E5" t="n">
-        <v>109.191579</v>
+        <v>109.204779</v>
       </c>
       <c r="F5" t="n">
-        <v>23.028424</v>
+        <v>23.050068</v>
       </c>
       <c r="G5" t="n">
-        <v>459.03</v>
+        <v>681.374</v>
       </c>
       <c r="H5" t="n">
-        <v>5055.45</v>
+        <v>813.074</v>
       </c>
       <c r="I5" t="n">
-        <v>7057.516</v>
+        <v>1761.292</v>
       </c>
       <c r="J5" t="n">
-        <v>7536.242</v>
+        <v>6365.579</v>
       </c>
       <c r="K5" t="n">
-        <v>0.855747</v>
+        <v>1.781176</v>
       </c>
     </row>
     <row r="6">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RC5</t>
+          <t>RC2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4558.575</v>
+        <v>108.952</v>
       </c>
       <c r="E6" t="n">
-        <v>109.237801</v>
+        <v>109.184079</v>
       </c>
       <c r="F6" t="n">
-        <v>23.068897</v>
+        <v>23.034724</v>
       </c>
       <c r="G6" t="n">
-        <v>445.42</v>
+        <v>511.829</v>
       </c>
       <c r="H6" t="n">
-        <v>5297.917</v>
+        <v>2029.244</v>
       </c>
       <c r="I6" t="n">
-        <v>6152.221</v>
+        <v>2551.662</v>
       </c>
       <c r="J6" t="n">
-        <v>6708.04</v>
+        <v>6365.579</v>
       </c>
       <c r="K6" t="n">
-        <v>0.57673</v>
+        <v>1.781176</v>
       </c>
     </row>
     <row r="7">
@@ -4808,32 +4808,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RC6</t>
+          <t>RC2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7559.645</v>
+        <v>108.952</v>
       </c>
       <c r="E7" t="n">
-        <v>109.249175</v>
+        <v>109.204779</v>
       </c>
       <c r="F7" t="n">
-        <v>23.058282</v>
+        <v>23.049868</v>
       </c>
       <c r="G7" t="n">
-        <v>552.175</v>
+        <v>591.453</v>
       </c>
       <c r="H7" t="n">
-        <v>8265.189</v>
+        <v>2782.08</v>
       </c>
       <c r="I7" t="n">
-        <v>8854.871999999999</v>
+        <v>4139.223</v>
       </c>
       <c r="J7" t="n">
-        <v>9385.789000000001</v>
+        <v>6365.579</v>
       </c>
       <c r="K7" t="n">
-        <v>0.466721</v>
+        <v>1.781176</v>
       </c>
     </row>
     <row r="8">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4853,28 +4853,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7836.242</v>
+        <v>108.952</v>
       </c>
       <c r="E8" t="n">
-        <v>109.237801</v>
+        <v>109.184079</v>
       </c>
       <c r="F8" t="n">
-        <v>23.068897</v>
+        <v>23.034724</v>
       </c>
       <c r="G8" t="n">
-        <v>445.42</v>
+        <v>511.829</v>
       </c>
       <c r="H8" t="n">
-        <v>8575.584000000001</v>
+        <v>4376.277</v>
       </c>
       <c r="I8" t="n">
-        <v>9193.639999999999</v>
+        <v>5863.619</v>
       </c>
       <c r="J8" t="n">
-        <v>9749.459999999999</v>
+        <v>6365.579</v>
       </c>
       <c r="K8" t="n">
-        <v>0.504543</v>
+        <v>1.781176</v>
       </c>
     </row>
   </sheetData>
@@ -4888,7 +4888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W67"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="14" customWidth="1" style="8" min="1" max="2"/>
@@ -5036,10 +5036,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1718.246</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2534.914</v>
+        <v>816.669</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2534.914</v>
+        <v>816.669</v>
       </c>
       <c r="D6" t="n">
-        <v>2678.784</v>
+        <v>1001.501</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -5090,10 +5090,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2678.784</v>
+        <v>1001.501</v>
       </c>
       <c r="D7" t="n">
-        <v>3334.17</v>
+        <v>1574.961</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R04</t>
         </is>
       </c>
     </row>
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3334.17</v>
+        <v>1574.961</v>
       </c>
       <c r="D8" t="n">
-        <v>3478.04</v>
+        <v>1759.794</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3478.04</v>
+        <v>1759.794</v>
       </c>
       <c r="D9" t="n">
-        <v>3833.06</v>
+        <v>2114.814</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -5175,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>708.28</v>
+        <v>753.003</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>708.28</v>
+        <v>753.003</v>
       </c>
       <c r="D11" t="n">
-        <v>1231.292</v>
+        <v>1561.501</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -5226,10 +5226,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1231.292</v>
+        <v>1561.501</v>
       </c>
       <c r="D12" t="n">
-        <v>1560.608</v>
+        <v>1944.463</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R04</t>
         </is>
       </c>
     </row>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1720.342</v>
+        <v>1316.642</v>
       </c>
       <c r="D24" t="n">
-        <v>2533.783</v>
+        <v>2130.083</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2533.783</v>
+        <v>2130.083</v>
       </c>
       <c r="D25" t="n">
-        <v>2954.995</v>
+        <v>2551.294</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R05</t>
         </is>
       </c>
     </row>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2954.995</v>
+        <v>2551.294</v>
       </c>
       <c r="D26" t="n">
-        <v>3433.378</v>
+        <v>3029.678</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
     </row>
@@ -5704,10 +5704,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1560.608</v>
+        <v>2075.298</v>
       </c>
       <c r="D30" t="n">
-        <v>2313.61</v>
+        <v>2783.578</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2313.61</v>
+        <v>2783.578</v>
       </c>
       <c r="D31" t="n">
-        <v>3122.109</v>
+        <v>2924.76</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R02</t>
         </is>
       </c>
     </row>
@@ -5754,76 +5754,78 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3122.109</v>
+        <v>2924.76</v>
       </c>
       <c r="D32" t="n">
-        <v>3505.071</v>
+        <v>3168.629</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5033.107</v>
+        <v>3168.629</v>
       </c>
       <c r="D33" t="n">
-        <v>5978.973</v>
+        <v>3306.59</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5978.973</v>
+        <v>3306.59</v>
       </c>
       <c r="D34" t="n">
-        <v>7056.478</v>
+        <v>3635.905</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -5838,10 +5840,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7056.478</v>
+        <v>2114.814</v>
       </c>
       <c r="D35" t="n">
-        <v>7535.754</v>
+        <v>3060.679</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -5855,55 +5857,55 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2195.771</v>
+        <v>3060.679</v>
       </c>
       <c r="D36" t="n">
-        <v>3033.142</v>
+        <v>4138.185</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3033.142</v>
+        <v>4138.185</v>
       </c>
       <c r="D37" t="n">
-        <v>3654.499</v>
+        <v>4617.461</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -5918,10 +5920,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3654.499</v>
+        <v>2195.771</v>
       </c>
       <c r="D38" t="n">
-        <v>4161.727</v>
+        <v>3033.142</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5935,55 +5937,55 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2307.348</v>
+        <v>3033.142</v>
       </c>
       <c r="D39" t="n">
-        <v>3057.723</v>
+        <v>3654.499</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T16</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3057.723</v>
+        <v>3654.499</v>
       </c>
       <c r="D40" t="n">
-        <v>3237.56</v>
+        <v>4161.727</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -5994,24 +5996,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3237.56</v>
+        <v>2307.348</v>
       </c>
       <c r="D41" t="n">
-        <v>3915.456</v>
+        <v>3057.723</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>R03</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -6022,54 +6022,58 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3915.456</v>
+        <v>3057.723</v>
       </c>
       <c r="D42" t="n">
-        <v>4318.065</v>
+        <v>3382.168</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>R02</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>7426.441</v>
+        <v>3382.168</v>
       </c>
       <c r="D43" t="n">
-        <v>8267.438</v>
+        <v>3596.126</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6078,10 +6082,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8267.438</v>
+        <v>3596.126</v>
       </c>
       <c r="D44" t="n">
-        <v>8852.623</v>
+        <v>3654.693</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -6090,40 +6094,42 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>R06</t>
+          <t>R02</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8852.623</v>
+        <v>3654.693</v>
       </c>
       <c r="D45" t="n">
-        <v>9351.656000000001</v>
+        <v>3915.456</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6132,10 +6138,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4360.4</v>
+        <v>3915.456</v>
       </c>
       <c r="D46" t="n">
-        <v>5298.417</v>
+        <v>4318.065</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -6149,61 +6155,61 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5298.417</v>
+        <v>2711.957</v>
       </c>
       <c r="D47" t="n">
-        <v>5947.611</v>
+        <v>3512.082</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>R05</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T18</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5947.611</v>
+        <v>3512.082</v>
       </c>
       <c r="D48" t="n">
-        <v>6543.664</v>
+        <v>4102.002</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>R06</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6212,10 +6218,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4272.376</v>
+        <v>4102.002</v>
       </c>
       <c r="D49" t="n">
-        <v>5055.817</v>
+        <v>4541.734</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -6229,61 +6235,61 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5055.817</v>
+        <v>3242.02</v>
       </c>
       <c r="D50" t="n">
-        <v>5447.028</v>
+        <v>4180.037</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>R04</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5447.028</v>
+        <v>4180.037</v>
       </c>
       <c r="D51" t="n">
-        <v>5925.412</v>
+        <v>4829.231</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6292,10 +6298,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4459.169</v>
+        <v>4829.231</v>
       </c>
       <c r="D52" t="n">
-        <v>5300.166</v>
+        <v>5425.284</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -6309,87 +6315,89 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5300.166</v>
+        <v>3593.203</v>
       </c>
       <c r="D53" t="n">
-        <v>5885.351</v>
+        <v>4376.644</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>R05</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>5885.351</v>
+        <v>4376.644</v>
       </c>
       <c r="D54" t="n">
-        <v>6384.384</v>
+        <v>4431.47</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>T21</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3874.145</v>
+        <v>4431.47</v>
       </c>
       <c r="D55" t="n">
-        <v>5299.03</v>
+        <v>4714.048</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>R07</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>T21</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6398,10 +6406,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5299.03</v>
+        <v>4714.048</v>
       </c>
       <c r="D56" t="n">
-        <v>6151.179</v>
+        <v>4767.856</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -6410,14 +6418,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>R03</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>T21</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6426,10 +6434,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6151.179</v>
+        <v>4767.856</v>
       </c>
       <c r="D57" t="n">
-        <v>6565.275</v>
+        <v>5246.239</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -6443,7 +6451,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6452,10 +6460,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4252.958</v>
+        <v>3809.056</v>
       </c>
       <c r="D58" t="n">
-        <v>5055.949</v>
+        <v>4650.053</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -6469,7 +6477,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6478,10 +6486,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5055.949</v>
+        <v>4650.053</v>
       </c>
       <c r="D59" t="n">
-        <v>5954.351</v>
+        <v>5235.238</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -6490,14 +6498,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>R03</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6506,10 +6514,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5954.351</v>
+        <v>5235.238</v>
       </c>
       <c r="D60" t="n">
-        <v>6456.282</v>
+        <v>5734.271</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -6523,7 +6531,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6532,10 +6540,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>7714.721</v>
+        <v>3814.962</v>
       </c>
       <c r="D61" t="n">
-        <v>8577.081</v>
+        <v>5239.848</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -6549,7 +6557,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6558,10 +6566,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8577.081</v>
+        <v>5239.848</v>
       </c>
       <c r="D62" t="n">
-        <v>8685.716</v>
+        <v>6091.997</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -6570,42 +6578,40 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>R06</t>
+          <t>R03</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>中继</t>
+          <t>直连</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8685.716</v>
+        <v>6091.997</v>
       </c>
       <c r="D63" t="n">
-        <v>9192.144</v>
+        <v>6506.093</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>中继</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>R07</t>
-        </is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6614,10 +6620,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9192.144</v>
+        <v>4161.727</v>
       </c>
       <c r="D64" t="n">
-        <v>9594.375</v>
+        <v>4964.718</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -6631,33 +6637,35 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T24</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>直连</t>
+          <t>中继</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5596.663</v>
+        <v>4964.718</v>
       </c>
       <c r="D65" t="n">
-        <v>6396.789</v>
+        <v>4996.697</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v/>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>T24</t>
+          <t>T22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6666,10 +6674,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6396.789</v>
+        <v>4996.697</v>
       </c>
       <c r="D66" t="n">
-        <v>6986.709</v>
+        <v>5831.14</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -6678,33 +6686,221 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>R07</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>T22</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>5831.14</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5863.119</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>T22</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>5863.119</v>
+      </c>
+      <c r="D68" t="n">
+        <v>6365.051</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>T23</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4541.734</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5382.731</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>T23</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>5382.731</v>
+      </c>
+      <c r="D70" t="n">
+        <v>5967.916</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>T23</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>5967.916</v>
+      </c>
+      <c r="D71" t="n">
+        <v>6466.949</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>T24</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>6986.709</v>
-      </c>
-      <c r="D67" t="n">
-        <v>7426.441</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>直连</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>4617.461</v>
+      </c>
+      <c r="D72" t="n">
+        <v>5479.822</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>5479.822</v>
+      </c>
+      <c r="D73" t="n">
+        <v>6094.884</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>中继</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>6094.884</v>
+      </c>
+      <c r="D74" t="n">
+        <v>6497.115</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>直连</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
         <v/>
       </c>
     </row>
@@ -6801,14 +6997,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S008,S010,S011,S013,S014</t>
+          <t>S001,S002,S003,S004,S005,S006,S007,S008,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -6817,7 +7013,7 @@
         <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -6826,7 +7022,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -6838,7 +7034,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S009,S012,S015</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -6854,7 +7050,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -6863,7 +7059,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -6875,32 +7071,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S001,S002,S003,S004,S005,S006,S007,S010,S013,S014</t>
+          <t>S001,S002,S003,S004,S005,S006,S008,S010,S011,S012,S013,S014,S015</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -6912,26 +7108,26 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S008,S011</t>
+          <t>S007</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -6949,7 +7145,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S009,S012,S015</t>
+          <t>S009</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -6965,7 +7161,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6974,7 +7170,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
